--- a/results/job_matches_2026-09-10.xlsx
+++ b/results/job_matches_2026-09-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c1021a7b6a47a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb7f514c771de53</t>
+          <t>https://www.indeed.com/viewjob?jk=76c1021a7b6a47a3</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb7f514c771de53</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94535e52011728f</t>
+          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
+          <t>https://www.indeed.com/viewjob?jk=d94535e52011728f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TP-LINK</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, Hadoop, Hive, Sqoop, Spark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ca6ce91460b142</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Entarian</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b64978da5029f9c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8571eee74fa37144</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8571eee74fa37144</t>
+          <t>https://www.indeed.com/viewjob?jk=5306f5b43c1fe61a</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5306f5b43c1fe61a</t>
+          <t>https://www.indeed.com/viewjob?jk=6250b6d758b24165</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6250b6d758b24165</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd7cac2745190a8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP Python Data Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daaa8d1691a560b0</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b5fdfad3bcb351</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6f67526f506467e7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a3b9d686f61d33</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4de186a738732d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9fc3a90bd6ff881</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b978d27219d3d6a7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
+          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=10a3b9d686f61d33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Malibu Boats</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Loudon, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, MySQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
+          <t>https://www.indeed.com/viewjob?jk=175e6757af0bf2a6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615042a0b73fe9a</t>
+          <t>https://www.indeed.com/viewjob?jk=22fc60c81741f7ff</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - On-site, Durham, NC</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,102 +1266,102 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f404d54522769c</t>
+          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, IAM, Azure, Databricks, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c524d2ec156b31a3</t>
+          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer - xLT</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Data Lake Storage, Event Hubs, Dataflow, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24527e4fd5602bee</t>
+          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
+          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92fecc97a72ee4bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps/SRE Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188b1c3ac78beb01</t>
+          <t>https://www.indeed.com/viewjob?jk=8615042a0b73fe9a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Data Solutions Engineer - On-site, Durham, NC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669507442371cba5</t>
+          <t>https://www.indeed.com/viewjob?jk=37f404d54522769c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Stier Solutions</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Franklin, IN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8936f30be432de75</t>
+          <t>https://www.indeed.com/viewjob?jk=f528980ed0c8d2a7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mid/Senior-level GoLang Data Engineer</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f02dc8343f177b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a75da7f8d02636</t>
+          <t>https://www.indeed.com/viewjob?jk=3376613ab3f984d6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f69e0df39814636</t>
+          <t>https://www.indeed.com/viewjob?jk=294751ce2ccb4446</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a10b5deeed57fb5</t>
+          <t>https://www.indeed.com/viewjob?jk=41caab3acdd93a76</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Automation QE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e79a4a8aebbe0c</t>
+          <t>https://www.indeed.com/viewjob?jk=06496f73c79ac629</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac087a17c748782d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74172d3e99aa20dd</t>
+          <t>https://www.indeed.com/viewjob?jk=12312783d59ed413</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75e52ec0c2d0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d781344d29a08f9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior DevOps/SRE Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e442b1efc55de33f</t>
+          <t>https://www.indeed.com/viewjob?jk=188b1c3ac78beb01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Stier Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Franklin, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd2755f6f579f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=8936f30be432de75</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Data Solutions</t>
+          <t>Mid/Senior-level GoLang Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coral Springs, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,137 +1931,137 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c874c000ec76150</t>
+          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate, Data Operations</t>
+          <t>Senior Full Stack Java Developer (contract)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bank OZK</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643dff32a837e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=1df4bb06b967bbfd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Senior Business Data Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mutual of Omaha Mortgage</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c4f20a82a492aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Guidewire Developer (PolicyCenter)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3929e9d9282e947</t>
+          <t>https://www.indeed.com/viewjob?jk=67a75da7f8d02636</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f69e0df39814636</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Fraud Data Governance)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa247b105a8195a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a10b5deeed57fb5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Business Intelligence Analyst)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4613876632d673e6</t>
+          <t>https://www.indeed.com/viewjob?jk=17e79a4a8aebbe0c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Associate Data Engineer)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
+          <t>https://www.indeed.com/viewjob?jk=ac087a17c748782d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b7b991704ba53d</t>
+          <t>https://www.indeed.com/viewjob?jk=74172d3e99aa20dd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0de49c5b0005920d</t>
+          <t>https://www.indeed.com/viewjob?jk=fc75e52ec0c2d0a5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Back End Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
+          <t>https://www.indeed.com/viewjob?jk=4d781344d29a08f9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb93157183e3b612</t>
+          <t>https://www.indeed.com/viewjob?jk=e442b1efc55de33f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=223035fc7a8a7be0</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd2755f6f579f1e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solution Engineer - Remote</t>
+          <t>Mid-Level Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Crisis Text Line</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=549bd67dfaf059ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer – Cloud Data Solutions</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hub Group</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Coral Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,49 +2421,49 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef7cf9602f7515</t>
+          <t>https://www.indeed.com/viewjob?jk=4c874c000ec76150</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Security Engineer, Detection &amp; Response</t>
+          <t>Associate, Data Operations</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aircall</t>
+          <t>Bank OZK</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, IAM, RDS, Azure, Databricks, GCP, Scala, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
+          <t>https://www.indeed.com/viewjob?jk=e643dff32a837e1d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Statistician</t>
+          <t>Sr. Data Engineer, Datawarehouse, Service &amp; Tools</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2477,46 +2477,46 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a59b98e9d736a6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a9723e44861c14</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bdfee16835ece7</t>
+          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Azure Architect - Managed Services</t>
+          <t>Azure Cloud Solutions Architect - Remote in US</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Quisitive</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Scala, MySQL, Azure Cosmos DB, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d9680f06d024613</t>
+          <t>https://www.indeed.com/viewjob?jk=32b410cde48b67dc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Base Administrator</t>
+          <t>Summer Associate Internship (Fraud Data Governance)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Big D Companies</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa247b105a8195a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI/ML Developer</t>
+          <t>Summer Associate Internship (Business Intelligence Analyst)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
+          <t>https://www.indeed.com/viewjob?jk=4613876632d673e6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ETL Tester with AI Exp</t>
+          <t>Data Product Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c20717958974031</t>
+          <t>https://www.indeed.com/viewjob?jk=573efb398da27847</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VSCO</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Kafka, Snowflake, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c9e239c02c708b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a84f1785db094f6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MySQL, dbt, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
+          <t>https://www.indeed.com/viewjob?jk=dd45ffb84690ca5d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Systems Engineer - IT Data Management</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b7b991704ba53d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Summer Associate Internship (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Data Engineer)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, ETL, ELT, Python</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,102 +2841,102 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea20d1b92e7c4c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0de49c5b0005920d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c91100957431</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdf608d1b4f491a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud Network Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KINECTIVE</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c91e3acfe1355358</t>
+          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Solutions Architect - Digital Native Business (Healthtech)</t>
+          <t>Software Engineer - Access Management (Java Full Stack)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
+          <t>Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11453f277a40e0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT Analyst III - Senior Test Automation Engineer</t>
+          <t>AI Architect (Job ID 3021788)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>State of Utah</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, AWS CodePipeline, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25024b299f02a2f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f0843f4b858b32d0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Engineer, Enterprise AI Platform</t>
+          <t>Cloud Back End Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Camping World</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
+          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Engineer, Enterprise AI Platform</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Camping World</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee18a654788e5998</t>
+          <t>https://www.indeed.com/viewjob?jk=eb93157183e3b612</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Evinova</t>
+          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Kafka, PostgreSQL, MongoDB, DynamoDB, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0631723e82c79799</t>
+          <t>https://www.indeed.com/viewjob?jk=c333cc6dde3f595b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Network Support &amp; Automation Engineer</t>
+          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,42 +3121,1197 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=721f751b91f07d44</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e866ca403b7a08</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. DevOps Infrastructure Engineer (AWS, Terraform, Cloud Networking)</t>
+          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bac87d7854fb47ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>a16z</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b859f6678b66ccda</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>a16z</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=569965346561f598</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>a16z</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e6e4382e04392bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>McKesson</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=223035fc7a8a7be0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Data Engineer I</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>ZincFive</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Tualatin, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, ETL</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a103bc6ce2d7b66</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>University of North Carolina at Greensboro</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Greensboro, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=241fedf4f4795a9c</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Data engineer- Sr Consultant</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Data &amp; Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Hub Group</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7ef7cf9602f7515</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Data Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d28e6b695048282</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AI Systems &amp; Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>BWX Technologies</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Oak Ridge, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Spark, Scala, Kafka, ELT, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72960e997f8affed</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ADT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78b145be092bbc45</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Data Statistician</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a59b98e9d736a6c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Databricks Architect</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24bdfee16835ece7</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer, Detection &amp; Response</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Aircall</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Athena, IAM, RDS, Azure, Databricks, GCP, Scala, Splunk</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AI/ML Developer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Mars Technominds</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ETL Tester with AI Exp</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
           <t>Chicago, IL, US USA</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c20717958974031</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Base Administrator</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Big D Companies</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>VSCO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Kafka, Snowflake, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4c9e239c02c708b</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AWS DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>The Consortium Inc.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, MySQL, dbt, CI/CD, Terraform, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>XCimer Energy</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
         <v>10.4</v>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4464a121a8f2d266</t>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de8b51b1b9068a38</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ImagineX Consulting</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Athena, RDS, Spark, Scala, Dimensional Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd4c4d67f0e8834</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Systems Engineer - IT Data Management</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>AutoZone</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Summer Associate Internship (Data Engineer)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Navy Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Vienna, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, ETL, ELT, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea20d1b92e7c4c0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sr Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Happen Bank</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2390c91100957431</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sr Cloud Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Happen Bank</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - Summer Intern 2027</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>S&amp;P Global</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Athena, S3, Spark, Scala, MLOps, Jenkins, Docker, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=932faec898cf8b5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior AWS Integration Developer - Remote US Position</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7650144ccb1d9294</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior AWS Integration Developer - Remote US Position</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28c061b38565c9ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Engineer, Enterprise AI Platform</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Camping World</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>AI Engineer, Enterprise AI Platform</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Camping World</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Lincolnshire, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee18a654788e5998</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-10.xlsx
+++ b/results/job_matches_2026-09-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
+          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
+          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c1021a7b6a47a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,129 +671,129 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb7f514c771de53</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd7cac2745190a8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d94535e52011728f</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b5fdfad3bcb351</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4de186a738732d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8571eee74fa37144</t>
+          <t>https://www.indeed.com/viewjob?jk=a9fc3a90bd6ff881</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,77 +836,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5306f5b43c1fe61a</t>
+          <t>https://www.indeed.com/viewjob?jk=6f67526f506467e7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Entarian</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Scala, Kafka, Polars, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6250b6d758b24165</t>
+          <t>https://www.indeed.com/viewjob?jk=b978d27219d3d6a7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd7cac2745190a8</t>
+          <t>https://www.indeed.com/viewjob?jk=10a3b9d686f61d33</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b5fdfad3bcb351</t>
+          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f67526f506467e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4de186a738732d</t>
+          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9fc3a90bd6ff881</t>
+          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b978d27219d3d6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Malibu Boats</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Loudon, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, MySQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a3b9d686f61d33</t>
+          <t>https://www.indeed.com/viewjob?jk=175e6757af0bf2a6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Malibu Boats</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Loudon, TN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, MySQL, Dimensional Modeling</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175e6757af0bf2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=8615042a0b73fe9a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Sr Developer - Java (POS)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22fc60c81741f7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e7519e1318081914</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Solutions Engineer - On-site, Durham, NC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>PowerSecure Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
+          <t>https://www.indeed.com/viewjob?jk=37f404d54522769c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f528980ed0c8d2a7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Automation QE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
+          <t>https://www.indeed.com/viewjob?jk=06496f73c79ac629</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f02dc8343f177b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
+          <t>https://www.indeed.com/viewjob?jk=3376613ab3f984d6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615042a0b73fe9a</t>
+          <t>https://www.indeed.com/viewjob?jk=294751ce2ccb4446</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - On-site, Durham, NC</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f404d54522769c</t>
+          <t>https://www.indeed.com/viewjob?jk=41caab3acdd93a76</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f528980ed0c8d2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f02dc8343f177b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3376613ab3f984d6</t>
+          <t>https://www.indeed.com/viewjob?jk=12312783d59ed413</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Senior DevOps/SRE Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294751ce2ccb4446</t>
+          <t>https://www.indeed.com/viewjob?jk=188b1c3ac78beb01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41caab3acdd93a76</t>
+          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Automation QE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stier Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Franklin, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06496f73c79ac629</t>
+          <t>https://www.indeed.com/viewjob?jk=8936f30be432de75</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid/Senior-level GoLang Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
+          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Java Developer (contract)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12312783d59ed413</t>
+          <t>https://www.indeed.com/viewjob?jk=1df4bb06b967bbfd</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
+          <t>https://www.indeed.com/viewjob?jk=2a10b5deeed57fb5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps/SRE Engineer</t>
+          <t>Senior Business Data Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mutual of Omaha Mortgage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188b1c3ac78beb01</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stier Solutions</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Franklin, IN, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8936f30be432de75</t>
+          <t>https://www.indeed.com/viewjob?jk=67a75da7f8d02636</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mid/Senior-level GoLang Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f69e0df39814636</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer (contract)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df4bb06b967bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=17e79a4a8aebbe0c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Business Data Analyst</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Mortgage</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
+          <t>https://www.indeed.com/viewjob?jk=ac087a17c748782d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a75da7f8d02636</t>
+          <t>https://www.indeed.com/viewjob?jk=74172d3e99aa20dd</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f69e0df39814636</t>
+          <t>https://www.indeed.com/viewjob?jk=fc75e52ec0c2d0a5</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a10b5deeed57fb5</t>
+          <t>https://www.indeed.com/viewjob?jk=4d781344d29a08f9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e79a4a8aebbe0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e442b1efc55de33f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac087a17c748782d</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd2755f6f579f1e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Sr. Data Engineer, Datawarehouse, Service &amp; Tools</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74172d3e99aa20dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a9723e44861c14</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Software Engineer – Cloud Data Solutions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Coral Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75e52ec0c2d0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c874c000ec76150</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Mid-Level Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Crisis Text Line</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,19 +2281,19 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d781344d29a08f9</t>
+          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Azure Cloud Solutions Architect - Remote in US</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Scala, MySQL, Azure Cosmos DB, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e442b1efc55de33f</t>
+          <t>https://www.indeed.com/viewjob?jk=32b410cde48b67dc</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd2755f6f579f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Crisis Text Line</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdf608d1b4f491a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Data Solutions</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Coral Springs, FL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,102 +2421,102 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c874c000ec76150</t>
+          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate, Data Operations</t>
+          <t>Summer Associate Internship (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bank OZK</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e643dff32a837e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Datawarehouse, Service &amp; Tools</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a9723e44861c14</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b7b991704ba53d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Data Product Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=573efb398da27847</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Architect - Remote in US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Scala, MySQL, Azure Cosmos DB, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b410cde48b67dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0de49c5b0005920d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Fraud Data Governance)</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa247b105a8195a</t>
+          <t>https://www.indeed.com/viewjob?jk=7a84f1785db094f6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Business Intelligence Analyst)</t>
+          <t>Cloud Back End Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Data Modeling, Dimension Tables, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4613876632d673e6</t>
+          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Product Engineer (Databricks)</t>
+          <t>Software Engineer - Access Management (Java Full Stack)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
+          <t>Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573efb398da27847</t>
+          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>AI Architect (Job ID 3021788)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a84f1785db094f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f0843f4b858b32d0</t>
         </is>
       </c>
     </row>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b7b991704ba53d</t>
+          <t>https://www.indeed.com/viewjob?jk=223035fc7a8a7be0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Associate Data Engineer)</t>
+          <t>Senior Software Engineer I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
+          <t>https://www.indeed.com/viewjob?jk=eb93157183e3b612</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0de49c5b0005920d</t>
+          <t>https://www.indeed.com/viewjob?jk=569965346561f598</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdf608d1b4f491a</t>
+          <t>https://www.indeed.com/viewjob?jk=b859f6678b66ccda</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6e4382e04392bb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer - Access Management (Java Full Stack)</t>
+          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=c333cc6dde3f595b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Architect (Job ID 3021788)</t>
+          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0843f4b858b32d0</t>
+          <t>https://www.indeed.com/viewjob?jk=bac87d7854fb47ac</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud Back End Engineer</t>
+          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e866ca403b7a08</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Technology Development Program (TECDP) - Data &amp; Analytics Engineering Track - Start Date: July 12, 2027</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions, Maven</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb93157183e3b612</t>
+          <t>https://www.indeed.com/viewjob?jk=55e214b9daaa34f3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>ZincFive</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tualatin, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c333cc6dde3f595b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a103bc6ce2d7b66</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>University of North Carolina at Greensboro</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e866ca403b7a08</t>
+          <t>https://www.indeed.com/viewjob?jk=241fedf4f4795a9c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>Hub Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac87d7854fb47ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ef7cf9602f7515</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b859f6678b66ccda</t>
+          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
+          <t>Senior Data engineer- Sr Consultant</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=569965346561f598</t>
+          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6e4382e04392bb</t>
+          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=223035fc7a8a7be0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d28e6b695048282</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ZincFive</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tualatin, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a103bc6ce2d7b66</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Statistician</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>University of North Carolina at Greensboro</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241fedf4f4795a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=a59b98e9d736a6c8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data engineer- Sr Consultant</t>
+          <t>AI Systems &amp; Solutions Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BWX Technologies</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, Spark, Scala, Kafka, ELT, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=72960e997f8affed</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=78b145be092bbc45</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>VSCO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>AWS, IAM, RDS, Kafka, Snowflake, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c9e239c02c708b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Scala, Snowflake, MySQL, dbt, CI/CD, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
+          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hub Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef7cf9602f7515</t>
+          <t>https://www.indeed.com/viewjob?jk=24bdfee16835ece7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer</t>
+          <t>Senior Security Engineer, Detection &amp; Response</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Aircall</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+          <t>AWS, Lambda, Athena, IAM, RDS, Azure, Databricks, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d28e6b695048282</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI Systems &amp; Solutions Engineer</t>
+          <t>AI/ML Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, ELT, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72960e997f8affed</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>ETL Tester with AI Exp</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b145be092bbc45</t>
+          <t>https://www.indeed.com/viewjob?jk=4c20717958974031</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Statistician</t>
+          <t>Data Base Administrator</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Big D Companies</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a59b98e9d736a6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Systems Engineer - IT Data Management</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bdfee16835ece7</t>
+          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Security Engineer, Detection &amp; Response</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Aircall</t>
+          <t>XCimer Energy</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, IAM, RDS, Azure, Databricks, GCP, Scala, Splunk</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
+          <t>https://www.indeed.com/viewjob?jk=de8b51b1b9068a38</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI/ML Developer</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
+          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ETL Tester with AI Exp</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
+          <t>AWS, Glue, Athena, RDS, Spark, Scala, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c20717958974031</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd4c4d67f0e8834</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Base Administrator</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Big D Companies</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
+          <t>https://www.indeed.com/viewjob?jk=2390c91100957431</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Senior AWS Integration Developer - Remote US Position</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VSCO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Kafka, Snowflake, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c9e239c02c708b</t>
+          <t>https://www.indeed.com/viewjob?jk=7650144ccb1d9294</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Senior AWS Integration Developer - Remote US Position</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MySQL, dbt, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
+          <t>https://www.indeed.com/viewjob?jk=28c061b38565c9ee</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Summer Associate Internship (Data Engineer)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>XCimer Energy</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8b51b1b9068a38</t>
+          <t>https://www.indeed.com/viewjob?jk=ea20d1b92e7c4c0a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer, Enterprise AI Platform</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Camping World</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Spark, Scala, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd4c4d67f0e8834</t>
+          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Systems Engineer - IT Data Management</t>
+          <t>AI Engineer, Enterprise AI Platform</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Camping World</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
+          <t>https://www.indeed.com/viewjob?jk=ee18a654788e5998</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Data Engineer)</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,262 +4056,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, ETL, ELT, Python</t>
+          <t>AWS, Lambda, S3, Scala, Kafka, MongoDB, DynamoDB, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea20d1b92e7c4c0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Happen Bank</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c91100957431</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Happen Bank</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Lehi, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer - Summer Intern 2027</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>S&amp;P Global</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Athena, S3, Spark, Scala, MLOps, Jenkins, Docker, Jenkins, Airflow</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=932faec898cf8b5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior AWS Integration Developer - Remote US Position</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>McKinney, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7650144ccb1d9294</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Senior AWS Integration Developer - Remote US Position</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>McKinney, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28c061b38565c9ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>AI Engineer, Enterprise AI Platform</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Camping World</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>AI Engineer, Enterprise AI Platform</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Camping World</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Lincolnshire, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee18a654788e5998</t>
+          <t>https://www.indeed.com/viewjob?jk=07909a893cd39d21</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-10.xlsx
+++ b/results/job_matches_2026-09-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>HomeServices of America</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
+          <t>https://www.indeed.com/viewjob?jk=dece858441573583</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
+          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,52 +626,52 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d6c2efe2d967ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, RDS, Databricks, Kafka, Snowflake</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bc8d7737feba10</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b5fdfad3bcb351</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd7cac2745190a8</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4de186a738732d</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b5fdfad3bcb351</t>
+          <t>https://www.indeed.com/viewjob?jk=a9fc3a90bd6ff881</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4de186a738732d</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd7cac2745190a8</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9fc3a90bd6ff881</t>
+          <t>https://www.indeed.com/viewjob?jk=6f67526f506467e7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f67526f506467e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b978d27219d3d6a7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b978d27219d3d6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
         </is>
       </c>
     </row>
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
+          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
+          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Malibu Boats</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Loudon, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, MySQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
+          <t>https://www.indeed.com/viewjob?jk=175e6757af0bf2a6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Malibu Boats</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Loudon, TN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, MySQL, Dimensional Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175e6757af0bf2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=22fc60c81741f7ff</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Developer - Java (POS)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615042a0b73fe9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7519e1318081914</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Developer - Java (POS)</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7519e1318081914</t>
+          <t>https://www.indeed.com/viewjob?jk=f528980ed0c8d2a7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer - On-site, Durham, NC</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PowerSecure Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37f404d54522769c</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f02dc8343f177b</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f528980ed0c8d2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3376613ab3f984d6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Automation QE</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06496f73c79ac629</t>
+          <t>https://www.indeed.com/viewjob?jk=294751ce2ccb4446</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f02dc8343f177b</t>
+          <t>https://www.indeed.com/viewjob?jk=41caab3acdd93a76</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Data Automation QE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,129 +1406,129 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3376613ab3f984d6</t>
+          <t>https://www.indeed.com/viewjob?jk=06496f73c79ac629</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294751ce2ccb4446</t>
+          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Senior Software Engineer – Full Stack / Backend / AI Systems</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41caab3acdd93a76</t>
+          <t>https://www.indeed.com/viewjob?jk=2ee3d7ccc5b43286</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
+          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DevOps/SRE Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188b1c3ac78beb01</t>
+          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps/SRE Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
+          <t>https://www.indeed.com/viewjob?jk=188b1c3ac78beb01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Java Developer (contract)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stier Solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Franklin, IN, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8936f30be432de75</t>
+          <t>https://www.indeed.com/viewjob?jk=1df4bb06b967bbfd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mid/Senior-level GoLang Data Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a10b5deeed57fb5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Stier Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Franklin, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df4bb06b967bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=8936f30be432de75</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid/Senior-level GoLang Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Inca Digital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
+          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Business Data Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Mutual of Omaha Mortgage</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a10b5deeed57fb5</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Business Data Analyst</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Mortgage</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
+          <t>https://www.indeed.com/viewjob?jk=ac087a17c748782d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac087a17c748782d</t>
+          <t>https://www.indeed.com/viewjob?jk=74172d3e99aa20dd</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74172d3e99aa20dd</t>
+          <t>https://www.indeed.com/viewjob?jk=fc75e52ec0c2d0a5</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75e52ec0c2d0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4d781344d29a08f9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d781344d29a08f9</t>
+          <t>https://www.indeed.com/viewjob?jk=e442b1efc55de33f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e442b1efc55de33f</t>
+          <t>https://www.indeed.com/viewjob?jk=9dd2755f6f579f1e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Sr. Data Engineer, Datawarehouse, Service &amp; Tools</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd2755f6f579f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a9723e44861c14</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Datawarehouse, Service &amp; Tools</t>
+          <t>Mid-Level Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Crisis Text Line</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a9723e44861c14</t>
+          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Data Solutions</t>
+          <t>Azure Cloud Solutions Architect - Remote in US</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Coral Springs, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Google Cloud Platform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Scala, MySQL, Azure Cosmos DB, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c874c000ec76150</t>
+          <t>https://www.indeed.com/viewjob?jk=32b410cde48b67dc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Crisis Text Line</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
+          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Architect - Remote in US</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Amherst, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Scala, MySQL, Azure Cosmos DB, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b410cde48b67dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c40cbadc2d21dbaf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,42 +2341,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f5698c0d5c0c74</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Brooklyn, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cdf608d1b4f491a</t>
+          <t>https://www.indeed.com/viewjob?jk=b59e4133cbdb8ecb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
+          <t>https://www.indeed.com/viewjob?jk=301dcda44c4f6fc9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Associate Data Engineer)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
+          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Summer Associate Internship (Associate Data Engineer)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Talend</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b7b991704ba53d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0de49c5b0005920d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a84f1785db094f6</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a84f1785db094f6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd45ffb84690ca5d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Back End Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b7b991704ba53d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - Access Management (Java Full Stack)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=0de49c5b0005920d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Architect (Job ID 3021788)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0843f4b858b32d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Cloud Back End Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd45ffb84690ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Architect (Job ID 3021788)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=223035fc7a8a7be0</t>
+          <t>https://www.indeed.com/viewjob?jk=f0843f4b858b32d0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Software Engineer - Access Management (Java Full Stack)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions, Maven</t>
+          <t>Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb93157183e3b612</t>
+          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
+          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=569965346561f598</t>
+          <t>https://www.indeed.com/viewjob?jk=c333cc6dde3f595b</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b859f6678b66ccda</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e866ca403b7a08</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
+          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6e4382e04392bb</t>
+          <t>https://www.indeed.com/viewjob?jk=bac87d7854fb47ac</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
+          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c333cc6dde3f595b</t>
+          <t>https://www.indeed.com/viewjob?jk=b859f6678b66ccda</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac87d7854fb47ac</t>
+          <t>https://www.indeed.com/viewjob?jk=569965346561f598</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
+          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e866ca403b7a08</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6e4382e04392bb</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ZincFive</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tualatin, OR, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, ETL</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a103bc6ce2d7b66</t>
+          <t>https://www.indeed.com/viewjob?jk=4b951826f674481d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>University of North Carolina at Greensboro</t>
+          <t>ZincFive</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Tualatin, OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241fedf4f4795a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a103bc6ce2d7b66</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hub Group</t>
+          <t>University of North Carolina at Greensboro</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef7cf9602f7515</t>
+          <t>https://www.indeed.com/viewjob?jk=241fedf4f4795a9c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Data engineer- Sr Consultant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
+          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data engineer- Sr Consultant</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d28e6b695048282</t>
+          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hub Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ef7cf9602f7515</t>
         </is>
       </c>
     </row>
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes, Git</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b145be092bbc45</t>
+          <t>https://www.indeed.com/viewjob?jk=24bdfee16835ece7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VSCO</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Kafka, Snowflake, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c9e239c02c708b</t>
+          <t>https://www.indeed.com/viewjob?jk=78b145be092bbc45</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>Data Reliability Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MySQL, dbt, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
+          <t>https://www.indeed.com/viewjob?jk=5d28e6b695048282</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Senior Security Engineer, Detection &amp; Response</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Aircall</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Athena, IAM, RDS, Azure, Databricks, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bdfee16835ece7</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Security Engineer, Detection &amp; Response</t>
+          <t>AI/ML Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Aircall</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, IAM, RDS, Azure, Databricks, GCP, Scala, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AI/ML Developer</t>
+          <t>ETL Tester with AI Exp</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c20717958974031</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ETL Tester with AI Exp</t>
+          <t>AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, MySQL, dbt, CI/CD, Terraform, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c20717958974031</t>
+          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Base Administrator</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Big D Companies</t>
+          <t>VSCO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Kafka, Snowflake, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06360615fbf9de3a</t>
+          <t>https://www.indeed.com/viewjob?jk=c4c9e239c02c708b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Systems Engineer - IT Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>XCimer Energy</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
+          <t>https://www.indeed.com/viewjob?jk=de8b51b1b9068a38</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>XCimer Energy</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Glue, Athena, RDS, Spark, Scala, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8b51b1b9068a38</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd4c4d67f0e8834</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Systems Engineer - IT Data Management</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
+          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Summer Associate Internship (Data Engineer)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Navy Federal Credit Union</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Spark, Scala, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd4c4d67f0e8834</t>
+          <t>https://www.indeed.com/viewjob?jk=ea20d1b92e7c4c0a</t>
         </is>
       </c>
     </row>
@@ -3863,17 +3863,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior AWS Integration Developer - Remote US Position</t>
+          <t>Sr Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Happen Bank</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7650144ccb1d9294</t>
+          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AWS Integration Developer - Remote US Position</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28c061b38565c9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=51b5c752bcea4a63</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Data Engineer)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea20d1b92e7c4c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=29c6c7d18ea19a8a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>AI Engineer, Enterprise AI Platform</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Camping World</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
+          <t>https://www.indeed.com/viewjob?jk=3008b2b65d88bbc4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AI Engineer, Enterprise AI Platform</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Camping World</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee18a654788e5998</t>
+          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,17 +4056,227 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e32a81cb68325f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6fa14d5b8cd87fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Samsara</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e793a447fb350e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sr Product Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, Scala, Kafka, MongoDB, DynamoDB, Jenkins, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=07909a893cd39d21</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior AWS Integration Developer - Remote US Position</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=28c061b38565c9ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior AWS Integration Developer - Remote US Position</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>McKinney, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7650144ccb1d9294</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Engineer, Enterprise AI Platform</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Camping World</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-10.xlsx
+++ b/results/job_matches_2026-09-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>29.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bedb030ec88c051</t>
+          <t>https://www.indeed.com/viewjob?jk=0a9ab035b419ae49</t>
         </is>
       </c>
     </row>
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
+          <t>https://www.indeed.com/viewjob?jk=eab311aee9088816</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=060cda39e6c67619</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
+          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b5fdfad3bcb351</t>
+          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4de186a738732d</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>(1112164) Senior Software Engineer - Java/AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9fc3a90bd6ff881</t>
+          <t>https://www.indeed.com/viewjob?jk=8e81425a0990a5a5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>(1112164) Senior Software Engineer - Java/AWS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd7cac2745190a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1ca06bddd5e551</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,77 +801,77 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f67526f506467e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8137b74f0acce5b3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b978d27219d3d6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=14f224257248a225</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd7cac2745190a8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a3b9d686f61d33</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b5fdfad3bcb351</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f67526f506467e7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1f4de186a738732d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
+          <t>https://www.indeed.com/viewjob?jk=a9fc3a90bd6ff881</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Cornerstone OnDemand</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b978d27219d3d6a7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
+          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Malibu Boats</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Loudon, TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, MySQL, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175e6757af0bf2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22fc60c81741f7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Developer - Java (POS)</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7519e1318081914</t>
+          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f528980ed0c8d2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f02dc8343f177b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Malibu Boats</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Loudon, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, MySQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3376613ab3f984d6</t>
+          <t>https://www.indeed.com/viewjob?jk=175e6757af0bf2a6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Sr. Environment Engineer - Oracle Platforms</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ventura Foods</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294751ce2ccb4446</t>
+          <t>https://www.indeed.com/viewjob?jk=22fc60c81741f7ff</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Sr Developer - Java (POS)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41caab3acdd93a76</t>
+          <t>https://www.indeed.com/viewjob?jk=e7519e1318081914</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Automation QE</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06496f73c79ac629</t>
+          <t>https://www.indeed.com/viewjob?jk=f528980ed0c8d2a7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
+          <t>https://www.indeed.com/viewjob?jk=c4f02dc8343f177b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack / Backend / AI Systems</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee3d7ccc5b43286</t>
+          <t>https://www.indeed.com/viewjob?jk=3376613ab3f984d6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
+          <t>https://www.indeed.com/viewjob?jk=294751ce2ccb4446</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
+          <t>https://www.indeed.com/viewjob?jk=41caab3acdd93a76</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12312783d59ed413</t>
+          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior DevOps/SRE Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188b1c3ac78beb01</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer (contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df4bb06b967bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=12312783d59ed413</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a10b5deeed57fb5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mid/Senior-level GoLang Data Engineer</t>
+          <t>Senior Full Stack Java Developer (contract)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Inca Digital</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a6235675ac15c</t>
+          <t>https://www.indeed.com/viewjob?jk=1df4bb06b967bbfd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Business Data Analyst</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Mortgage</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
+          <t>https://www.indeed.com/viewjob?jk=2f69e0df39814636</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Business Data Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Mutual of Omaha Mortgage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac087a17c748782d</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f69e0df39814636</t>
+          <t>https://www.indeed.com/viewjob?jk=2a10b5deeed57fb5</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74172d3e99aa20dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ac087a17c748782d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75e52ec0c2d0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=74172d3e99aa20dd</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d781344d29a08f9</t>
+          <t>https://www.indeed.com/viewjob?jk=fc75e52ec0c2d0a5</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e442b1efc55de33f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d781344d29a08f9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dd2755f6f579f1e</t>
+          <t>https://www.indeed.com/viewjob?jk=e442b1efc55de33f</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer</t>
+          <t>Azure Cloud Solutions Developer / Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Crisis Text Line</t>
+          <t>Doeren Mayhew CPAs and Advisors</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, SQL Server, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
+          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Architect - Remote in US</t>
+          <t>Mid-Level Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Crisis Text Line</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Scala, MySQL, Azure Cosmos DB, Power BI, CI/CD</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b410cde48b67dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Azure Cloud Solutions Architect - Remote in US</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Scala, MySQL, Azure Cosmos DB, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=32b410cde48b67dc</t>
         </is>
       </c>
     </row>
@@ -2428,25 +2428,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>US LBM Holdings</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
+          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Associate Data Engineer)</t>
+          <t>Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>Colaberry</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa822ad66fbbecb6</t>
+          <t>https://www.indeed.com/viewjob?jk=8afd4daee0cfbd6a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Product Engineer (Databricks)</t>
+          <t>Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colaberry</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573efb398da27847</t>
+          <t>https://www.indeed.com/viewjob?jk=feb309dc36a3ade0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a84f1785db094f6</t>
+          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Data Product Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd45ffb84690ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=573efb398da27847</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Talend</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8b7b991704ba53d</t>
+          <t>https://www.indeed.com/viewjob?jk=7a84f1785db094f6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0de49c5b0005920d</t>
+          <t>https://www.indeed.com/viewjob?jk=dd45ffb84690ca5d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>VRN Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6a06ecdadb7f76</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cloud Back End Engineer</t>
+          <t>AI Architect (Job ID 3021788)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=979c2d51bf327a22</t>
+          <t>https://www.indeed.com/viewjob?jk=f0843f4b858b32d0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Architect (Job ID 3021788)</t>
+          <t>Software Engineer - Access Management (Java Full Stack)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes</t>
+          <t>Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0843f4b858b32d0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Access Management (Java Full Stack)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bloomfield, CT, US USA</t>
+          <t>Morris Plains, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e214b9daaa34f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1edfbfa72a62d73c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b951826f674481d</t>
+          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ZincFive</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tualatin, OR, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a103bc6ce2d7b66</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae52bab9bde8833</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>University of North Carolina at Greensboro</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241fedf4f4795a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b951826f674481d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data engineer- Sr Consultant</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ZincFive</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tualatin, OR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a103bc6ce2d7b66</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>University of North Carolina at Greensboro</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=241fedf4f4795a9c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Data engineer- Sr Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
+          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
+          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hub Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef7cf9602f7515</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Statistician</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a59b98e9d736a6c8</t>
+          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Systems &amp; Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>Hub Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, ELT, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72960e997f8affed</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ef7cf9602f7515</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Data Reliability Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bdfee16835ece7</t>
+          <t>https://www.indeed.com/viewjob?jk=5d28e6b695048282</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>AI Systems &amp; Solutions Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>BWX Technologies</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes, Git</t>
+          <t>AWS, Spark, Scala, Kafka, ELT, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b145be092bbc45</t>
+          <t>https://www.indeed.com/viewjob?jk=72960e997f8affed</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer</t>
+          <t>Data Statistician</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+          <t>AWS, RDS, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d28e6b695048282</t>
+          <t>https://www.indeed.com/viewjob?jk=a59b98e9d736a6c8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Security Engineer, Detection &amp; Response</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Aircall</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, IAM, RDS, Azure, Databricks, GCP, Scala, Splunk</t>
+          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
+          <t>https://www.indeed.com/viewjob?jk=24bdfee16835ece7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI/ML Developer</t>
+          <t>Senior Security Engineer, Detection &amp; Response</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mars Technominds</t>
+          <t>Aircall</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, Athena, IAM, RDS, Azure, Databricks, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ETL Tester with AI Exp</t>
+          <t>AI/ML Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Mars Technominds</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c20717958974031</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer</t>
+          <t>ETL Tester with AI Exp</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, MySQL, dbt, CI/CD, Terraform, Git, Bitbucket</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e6bb06610c32bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4c20717958974031</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>XCimer Energy</t>
+          <t>Hallmark</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de8b51b1b9068a38</t>
+          <t>https://www.indeed.com/viewjob?jk=19d1b36881ddad57</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ImagineX Consulting</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, RDS, Spark, Scala, Dimensional Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd4c4d67f0e8834</t>
+          <t>https://www.indeed.com/viewjob?jk=1354b65cdd4f0090</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Systems Engineer - IT Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
+          <t>https://www.indeed.com/viewjob?jk=f2654e3bd2509e90</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Summer Associate Internship (Data Engineer)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Navy Federal Credit Union</t>
+          <t>XCimer Energy</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, ETL, ELT, Python</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea20d1b92e7c4c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=de8b51b1b9068a38</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Athena, RDS, Spark, Scala, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2390c91100957431</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd4c4d67f0e8834</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr Cloud Infrastructure Engineer</t>
+          <t>Systems Engineer - IT Data Management</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Happen Bank</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=410d6c6a010f035c</t>
+          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Full Stack Developer - .NET / Angular</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Transnational Software Services</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51b5c752bcea4a63</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2cf6fa97f7e112</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c6c7d18ea19a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=51b5c752bcea4a63</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3008b2b65d88bbc4</t>
+          <t>https://www.indeed.com/viewjob?jk=29c6c7d18ea19a8a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
+          <t>https://www.indeed.com/viewjob?jk=3008b2b65d88bbc4</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e32a81cb68325f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior AWS Integration Developer - Remote US Position</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e793a447fb350e6</t>
+          <t>https://www.indeed.com/viewjob?jk=28c061b38565c9ee</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, Kafka, MongoDB, DynamoDB, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07909a893cd39d21</t>
+          <t>https://www.indeed.com/viewjob?jk=9e32a81cb68325f0</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior AWS Integration Developer - Remote US Position</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28c061b38565c9ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0e793a447fb350e6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior AWS Integration Developer - Remote US Position</t>
+          <t>Sr. DevOps Infrastructure Engineer (AWS, Terraform, Cloud Networking)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>McKinney, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,42 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7650144ccb1d9294</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>AI Engineer, Enterprise AI Platform</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Camping World</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, ECS, Azure, GCP, Snowflake, Data Modeling, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d593ed18a7eaef04</t>
+          <t>https://www.indeed.com/viewjob?jk=fab84d04db02eee2</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-10.xlsx
+++ b/results/job_matches_2026-09-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Sr Data Integration Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>HomeServices of America</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.2</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery, Hadoop</t>
+          <t>AWS, Glue, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a9ab035b419ae49</t>
+          <t>https://www.indeed.com/viewjob?jk=dece858441573583</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Integration Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HomeServices of America</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dece858441573583</t>
+          <t>https://www.indeed.com/viewjob?jk=eab311aee9088816</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab311aee9088816</t>
+          <t>https://www.indeed.com/viewjob?jk=53e5ebe6596fd5cc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=060cda39e6c67619</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2550e31c47b05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e477f85009259a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f823b2967bc25ff</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>(1112754) Senior Software Engineer - Java/AWS Backend</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, RDS, Azure, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a935b5e2a0461ce9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f454c459d8715c2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, RDS, GCP, Hadoop, HDFS, Spark, Scala, Kafka, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
+          <t>https://www.indeed.com/viewjob?jk=060cda39e6c67619</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(1112164) Senior Software Engineer - Java/AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diversified Services Network</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e81425a0990a5a5</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfc77cb04c85546</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b1ca06bddd5e551</t>
+          <t>https://www.indeed.com/viewjob?jk=8e81425a0990a5a5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>(1112164) Senior Software Engineer - Java/AWS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Diversified Services Network</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8137b74f0acce5b3</t>
+          <t>https://www.indeed.com/viewjob?jk=8b1ca06bddd5e551</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Morgan WM Java + Python - C1 - Level</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f224257248a225</t>
+          <t>https://www.indeed.com/viewjob?jk=2237bdba45156557</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd7cac2745190a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8137b74f0acce5b3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6b5fdfad3bcb351</t>
+          <t>https://www.indeed.com/viewjob?jk=14f224257248a225</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f67526f506467e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c6b5fdfad3bcb351</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f4de186a738732d</t>
+          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Systems Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Malibu Boats</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Loudon, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Oracle, Dimensional Modeling, Kimball, Snowflake Schema, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, MySQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9fc3a90bd6ff881</t>
+          <t>https://www.indeed.com/viewjob?jk=175e6757af0bf2a6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Developer - Java (POS)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Mason, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b978d27219d3d6a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7519e1318081914</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>BI Developer - MicroStrategy/Tableau</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75989850372d9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f528980ed0c8d2a7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Sr. Databricks Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Finbott</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b78ae98ab2be932f</t>
+          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Software Engineer – Full Stack / Backend / AI Systems</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26ce66265b66e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2ee3d7ccc5b43286</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8191dfab6e9beaa</t>
+          <t>https://www.indeed.com/viewjob?jk=12312783d59ed413</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Full Stack Java Developer (contract)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0152f97e4d45e6e2</t>
+          <t>https://www.indeed.com/viewjob?jk=1df4bb06b967bbfd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala, Databricks Lakehouse, ETL</t>
+          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6579da7d14e000</t>
+          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Systems Engineer</t>
+          <t>Senior Business Data Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Malibu Boats</t>
+          <t>Mutual of Omaha Mortgage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Loudon, TN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Scala, Snowflake, SQL Server, MySQL, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175e6757af0bf2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Environment Engineer - Oracle Platforms</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ventura Foods</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Oracle, Splunk, DataOps, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22fc60c81741f7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Developer - Java (POS)</t>
+          <t>Sr. Data Engineer, Datawarehouse, Service &amp; Tools</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mason, OH, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7519e1318081914</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a9723e44861c14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Azure Cloud Solutions Developer / Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Doeren Mayhew CPAs and Advisors</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, SQL Server, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f528980ed0c8d2a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Mid-Level Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Crisis Text Line</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f02dc8343f177b</t>
+          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Senior Feature Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3376613ab3f984d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc268f2e08eed41b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Sr Data Scientist, Merchandising Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294751ce2ccb4446</t>
+          <t>https://www.indeed.com/viewjob?jk=89cf28164d2b44e1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BI Developer - MicroStrategy/Tableau</t>
+          <t>Azure Cloud Solutions Architect - Remote in US</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Scala, MySQL, Azure Cosmos DB, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41caab3acdd93a76</t>
+          <t>https://www.indeed.com/viewjob?jk=32b410cde48b67dc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Databricks Engineer</t>
+          <t>Data &amp; Business Intelligence Senior Associate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Finbott</t>
+          <t>KeyBank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Amherst, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215a62808c4ca701</t>
+          <t>https://www.indeed.com/viewjob?jk=c40cbadc2d21dbaf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Colaberry</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e821a7c8c592b96</t>
+          <t>https://www.indeed.com/viewjob?jk=8afd4daee0cfbd6a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Contract)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Colaberry</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fcfd83790c152b3</t>
+          <t>https://www.indeed.com/viewjob?jk=feb309dc36a3ade0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Epsilon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,137 +1686,137 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12312783d59ed413</t>
+          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hive, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ada96da7df4f88d</t>
+          <t>https://www.indeed.com/viewjob?jk=348bb65020d238ec</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Stier Solutions</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Franklin, IN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8936f30be432de75</t>
+          <t>https://www.indeed.com/viewjob?jk=700edad9dfcb975f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full Stack Java Developer (contract)</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Woodbridge, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df4bb06b967bbfd</t>
+          <t>https://www.indeed.com/viewjob?jk=3cb87de2d0210269</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Product Engineer (Databricks)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f69e0df39814636</t>
+          <t>https://www.indeed.com/viewjob?jk=573efb398da27847</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Business Data Analyst</t>
+          <t>Data Integration Engineer I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Mortgage</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,137 +1861,137 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77cb9bd37d11728</t>
+          <t>https://www.indeed.com/viewjob?jk=dd45ffb84690ca5d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a75da7f8d02636</t>
+          <t>https://www.indeed.com/viewjob?jk=4f16755404b284eb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Persistent Systems</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a10b5deeed57fb5</t>
+          <t>https://www.indeed.com/viewjob?jk=f12f5f159f8687e2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>VRN Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17e79a4a8aebbe0c</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6a06ecdadb7f76</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer - Access Management (Java Full Stack)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac087a17c748782d</t>
+          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>AI Architect (Job ID 3021788)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,102 +2036,102 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74172d3e99aa20dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f0843f4b858b32d0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc75e52ec0c2d0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>S3, RDS, Scala, Snowflake, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d781344d29a08f9</t>
+          <t>https://www.indeed.com/viewjob?jk=a41755acf2e74e13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e442b1efc55de33f</t>
+          <t>https://www.indeed.com/viewjob?jk=c333cc6dde3f595b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Datawarehouse, Service &amp; Tools</t>
+          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Data Lake Storage, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a9723e44861c14</t>
+          <t>https://www.indeed.com/viewjob?jk=c4e866ca403b7a08</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Developer / Engineer</t>
+          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Doeren Mayhew CPAs and Advisors</t>
+          <t>Andreessen Horowitz</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Scala, SQL Server, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16b1ba2fceeeff4</t>
+          <t>https://www.indeed.com/viewjob?jk=bac87d7854fb47ac</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mid-Level Data Engineer</t>
+          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Crisis Text Line</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d750ac4b97ebdec6</t>
+          <t>https://www.indeed.com/viewjob?jk=b859f6678b66ccda</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Azure Cloud Solutions Architect - Remote in US</t>
+          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Blob Storage, Scala, MySQL, Azure Cosmos DB, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,102 +2281,102 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32b410cde48b67dc</t>
+          <t>https://www.indeed.com/viewjob?jk=569965346561f598</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>a16z</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Amherst, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40cbadc2d21dbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=6e6e4382e04392bb</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Technology Development Program (TECDP) - Data &amp; Analytics Engineering Track - Start Date: July 12, 2027</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Bloomfield, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f5698c0d5c0c74</t>
+          <t>https://www.indeed.com/viewjob?jk=55e214b9daaa34f3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brooklyn, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59e4133cbdb8ecb</t>
+          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data &amp; Business Intelligence Senior Associate</t>
+          <t>Sr. Cloud Infrastructure &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KeyBank</t>
+          <t>Ambarella</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,54 +2421,54 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=301dcda44c4f6fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=5d92d093b53bf68d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>US LBM Cybersecurity Engineer – Azure DevSecOps</t>
+          <t>Senior Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>US LBM Holdings</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Snowflake, MongoDB, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008164574e63eb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=564e7d0106f9c065</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Contract)</t>
+          <t>Senior DevOps engineer.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Colaberry</t>
+          <t>Ayla Networks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2477,11 +2477,11 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MySQL, Cassandra, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afd4daee0cfbd6a</t>
+          <t>https://www.indeed.com/viewjob?jk=a77b42dadc3d64bb</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Contract)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Colaberry</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb309dc36a3ade0</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae52bab9bde8833</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Epsilon</t>
+          <t>Vantive</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=456814563675f6cd</t>
+          <t>https://www.indeed.com/viewjob?jk=4b951826f674481d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Product Engineer (Databricks)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ZincFive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tualatin, OR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, Spark, Scala, ELT, MLflow</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=573efb398da27847</t>
+          <t>https://www.indeed.com/viewjob?jk=8a103bc6ce2d7b66</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>University of North Carolina at Greensboro</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a84f1785db094f6</t>
+          <t>https://www.indeed.com/viewjob?jk=241fedf4f4795a9c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Integration Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Hub Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd45ffb84690ca5d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7ef7cf9602f7515</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VRN Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e6a06ecdadb7f76</t>
+          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Architect (Job ID 3021788)</t>
+          <t>Senior Data engineer- Sr Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Kafka, Oracle, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,137 +2736,137 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0843f4b858b32d0</t>
+          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer - Access Management (Java Full Stack)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, ETL, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc88f49ae19c3ea5</t>
+          <t>https://www.indeed.com/viewjob?jk=c740e2d589eb308c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab128e3501b51439</t>
+          <t>https://www.indeed.com/viewjob?jk=b853a7d928445871</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
+          <t>Senior Site Reliability Engineer II ** Remote EST Preferred</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Horsham, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c333cc6dde3f595b</t>
+          <t>https://www.indeed.com/viewjob?jk=b3bcb4fe5f29db11</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
+          <t>AI Systems &amp; Solutions Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>BWX Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oak Ridge, TN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Spark, Scala, Kafka, ELT, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e866ca403b7a08</t>
+          <t>https://www.indeed.com/viewjob?jk=72960e997f8affed</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
+          <t>Data Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Andreessen Horowitz</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac87d7854fb47ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5d28e6b695048282</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform (Partner 16, Partner 18)</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b859f6678b66ccda</t>
+          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer, Software Factory (Partner 16, Partner 18)</t>
+          <t>Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,102 +2981,102 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=569965346561f598</t>
+          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer, Systems (Partner 16, Partner 18)</t>
+          <t>Sr Enterprise Data Platform and Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>a16z</t>
+          <t>Academy Sports + Outdoors</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Katy, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, PostgreSQL, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e6e4382e04392bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7fe15b0b60a4d2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Technology Development Program (TECDP) - Data &amp; Analytics Engineering Track - Start Date: July 12, 2027</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Morris Plains, NJ, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, MongoDB, Cassandra, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1edfbfa72a62d73c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8c0277359b3cc2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer (remote)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Hallmark</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI, Git, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e60af316cfb20b16</t>
+          <t>https://www.indeed.com/viewjob?jk=19d1b36881ddad57</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer - Compensation Systems</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae52bab9bde8833</t>
+          <t>https://www.indeed.com/viewjob?jk=1354b65cdd4f0090</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Platform Engineer, IT - DevOps and Emerging Tech</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vantive</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b951826f674481d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2654e3bd2509e90</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Systems Engineer - IT Data Management</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ZincFive</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tualatin, OR, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, ETL</t>
+          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a103bc6ce2d7b66</t>
+          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>University of North Carolina at Greensboro</t>
+          <t>XCimer Energy</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Greensboro, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=241fedf4f4795a9c</t>
+          <t>https://www.indeed.com/viewjob?jk=de8b51b1b9068a38</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data engineer- Sr Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ImagineX Consulting</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Athena, RDS, Spark, Scala, Dimensional Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f50e943f0e086f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd4c4d67f0e8834</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Full Stack Developer - .NET / Angular</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Transnational Software Services</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0463821856273c4a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2cf6fa97f7e112</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior AWS Integration Developer - Remote US Position</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,137 +3331,137 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfc8b8f48b55687</t>
+          <t>https://www.indeed.com/viewjob?jk=28c061b38565c9ee</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Cassandra, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ac97ed953cb74f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hub Group</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7ef7cf9602f7515</t>
+          <t>https://www.indeed.com/viewjob?jk=51b5c752bcea4a63</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Reliability Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d28e6b695048282</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fa14d5b8cd87fc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Systems &amp; Solutions Engineer</t>
+          <t>Sr. DevOps Infrastructure Engineer (AWS, Terraform, Cloud Networking)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BWX Technologies</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oak Ridge, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, ELT, MLOps, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3470,776 +3470,6 @@
         </is>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=72960e997f8affed</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Statistician</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Tesla</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, ETL, MLOps, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a59b98e9d736a6c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Databricks Architect</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24bdfee16835ece7</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Security Engineer, Detection &amp; Response</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Aircall</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Athena, IAM, RDS, Azure, Databricks, GCP, Scala, Splunk</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae0266885ac8547</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>AI/ML Developer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Mars Technominds</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5d7e731531139c</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>ETL Tester with AI Exp</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, dbt, MLflow</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c20717958974031</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Infrastructure</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>VSCO</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Kafka, Snowflake, MySQL, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4c9e239c02c708b</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Engineer (remote)</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Hallmark</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Power BI, Git, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19d1b36881ddad57</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Engineer - Compensation Systems</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Sunbelt Rentals</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1354b65cdd4f0090</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Sunbelt Rentals</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Fort Mill, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2654e3bd2509e90</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>XCimer Energy</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Databricks Lakehouse, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de8b51b1b9068a38</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>ImagineX Consulting</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Athena, RDS, Spark, Scala, Dimensional Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd4c4d67f0e8834</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Systems Engineer - IT Data Management</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>AutoZone</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Dataflow, HBase, Kafka, Oracle, NoSQL, ETL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61e0074bda774516</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Full Stack Developer - .NET / Angular</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Transnational Software Services</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>S3, RDS, Azure, Scala, Kafka, SQL Server, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2cf6fa97f7e112</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51b5c752bcea4a63</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29c6c7d18ea19a8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3008b2b65d88bbc4</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a0920adba0ab6199</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fa14d5b8cd87fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Senior AWS Integration Developer - Remote US Position</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>McKinney, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=28c061b38565c9ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9e32a81cb68325f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLflow, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e793a447fb350e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Sr. DevOps Infrastructure Engineer (AWS, Terraform, Cloud Networking)</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Jenkins</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fab84d04db02eee2</t>
         </is>
